--- a/docs/xlsform-template/dcp-xlsform-roster-example.xlsx
+++ b/docs/xlsform-template/dcp-xlsform-roster-example.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,21 +27,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDE5F0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,11 +48,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,74 +415,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>label::English (en)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>label::Urdu (ur)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>label::Sindhi (sd)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>hint::English (en)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>relevant</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>constraint</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>constraint_message::English (en)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>appearance</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>calculation</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>repeat_count</t>
         </is>
@@ -512,21 +503,28 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>This form is REFUSED by the importer today. See docs/xlsform-template.md section 5.</t>
+          <t>A roster. This workbook imports with 0 errors and 0 warnings — see docs/xlsform-template.md section 5 for what an enumerator sees.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>یہ فارم فی الحال درآمد نہیں ہو سکتا۔</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>یہ فارم گھر کے افراد کی فہرست بناتا ہے۔</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>هي فارم گهر جي ڀاتين جي فهرست ٺاهي ٿو.</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -551,27 +549,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>هتي ڪيترا ماڻهو رهن ٿا؟</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Drives the roster below.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>${hh_size} &gt; 0 and ${hh_size} &lt;= 30</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>A household must have between 1 and 30 members.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -594,17 +599,24 @@
           <t>ضلع</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ضلعو</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -627,13 +639,20 @@
           <t>گھر کے افراد</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>گهر جا ڀاتي</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>${hh_size}</t>
         </is>
@@ -660,17 +679,24 @@
           <t>فرد کا نام</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ڀاتي جو نالو</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -693,25 +719,32 @@
           <t>عمر</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>عمر</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>${member_age} &gt;= 0 and ${member_age} &lt; 120</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Age must be between 0 and 119.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -734,17 +767,24 @@
           <t>سربراہ سے رشتہ</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>سربراهه سان رشتو</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -769,19 +809,26 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>ڇا اسڪول وڃي ٿو؟</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Relevance inside a repeat is evaluated per instance.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>${member_age} &gt;= 5 and ${member_age} &lt;= 18</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -799,6 +846,9 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -811,34 +861,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>list_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>label::English (en)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>label::Urdu (ur)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>label::Sindhi (sd)</t>
         </is>
       </c>
     </row>
@@ -863,6 +912,11 @@
           <t>ہاں</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ها</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -885,6 +939,11 @@
           <t>نہیں</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>نه</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -907,6 +966,11 @@
           <t>سربراہ</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>سربراهه</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -929,6 +993,11 @@
           <t>شریک حیات</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>زال يا مڙس</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -951,6 +1020,11 @@
           <t>بچہ</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ٻار</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -971,6 +1045,11 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>دیگر رشتہ دار</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ٻيو مائٽ</t>
         </is>
       </c>
     </row>
@@ -987,30 +1066,24 @@
   </sheetPr>
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>form_title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>form_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>default_language</t>
         </is>
@@ -1019,7 +1092,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DCP roster example (not importable yet)</t>
+          <t>DCP roster example</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
